--- a/01_Raw_data/Long. Log.xlsx
+++ b/01_Raw_data/Long. Log.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Howley_Bradford_Streams\Howley_Bradford_Streams\01_Raw_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B45F4243-09CA-446B-BF43-4662196FFD59}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B28B00C-E4B3-4E80-B3C2-F380B7F01D5E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-90" windowWidth="19380" windowHeight="10260" activeTab="1" xr2:uid="{64D2FBDD-F42D-4992-8C84-743158C68750}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{64D2FBDD-F42D-4992-8C84-743158C68750}"/>
   </bookViews>
   <sheets>
     <sheet name="Long. Log" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="20">
   <si>
     <t>Site</t>
   </si>
@@ -78,10 +78,22 @@
     <t>distance</t>
   </si>
   <si>
-    <t>RASTERVALU</t>
+    <t>Y_04.2025</t>
   </si>
   <si>
-    <t>Q_fraction</t>
+    <t>X_04.2025</t>
+  </si>
+  <si>
+    <t>RASTERVALU_04.2025</t>
+  </si>
+  <si>
+    <t>Q_fraction_04.2025</t>
+  </si>
+  <si>
+    <t>X_07.2025</t>
+  </si>
+  <si>
+    <t>Y_07.2025</t>
   </si>
 </sst>
 </file>
@@ -565,10 +577,12 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="20" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -625,6 +639,2829 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>5</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>dims!$C$2:$C$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1267.3699999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2467.91</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4497.8599999999997</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>6130.37</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>dims!$D$2:$D$6</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>17795000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>14519100</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>10249400</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1812340</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>138375</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-C0E7-49AA-9E39-EC01FEECDA68}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="232168704"/>
+        <c:axId val="232169184"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="232168704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="232169184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="232169184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="232168704"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>6</a:t>
+            </a:r>
+          </a:p>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>dims!$C$7:$C$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>9149.2199999999993</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7836.22</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5594.22</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>4518.92</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>390.63</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>dims!$D$7:$D$12</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="6"/>
+                <c:pt idx="0">
+                  <c:v>9204</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1355500</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1139580</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3131520</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>26276900</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>26315900</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AB08-4A5D-83DB-39468D1008F7}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="232168704"/>
+        <c:axId val="232169184"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="232168704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="232169184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="232169184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="232168704"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>9</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="38100" cap="rnd">
+              <a:noFill/>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:xVal>
+            <c:numRef>
+              <c:f>dims!$C$13:$C$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>904.88</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>2002.8</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>3140.96</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>8475.9599999999991</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>dims!$D$13:$D$17</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>19864100</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19268200</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>5821280</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1960760</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>262193</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-DABA-4836-8A52-D6A5282D9E83}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="232168704"/>
+        <c:axId val="232169184"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="232168704"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="232169184"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="232169184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="232168704"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style3.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>76200</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>14287</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>90487</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Chart 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B9B178BE-360F-DCE1-F134-8F0E345717AD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>85725</xdr:colOff>
+      <xdr:row>15</xdr:row>
+      <xdr:rowOff>171450</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>30</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="Chart 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{54FE5783-8D43-4874-B672-0836A7A96E86}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>16</xdr:col>
+      <xdr:colOff>466725</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>24</xdr:col>
+      <xdr:colOff>161925</xdr:colOff>
+      <xdr:row>21</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="5" name="Chart 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B938CB04-3014-4609-BC3B-5AF4D1B61D83}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr>
+          <a:graphicFrameLocks/>
+        </xdr:cNvGraphicFramePr>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -945,9 +3782,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E6546461-839F-424C-AB60-C569389E6220}">
   <dimension ref="A1:K85"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -982,7 +3819,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>9.1</v>
       </c>
@@ -996,7 +3833,7 @@
         <v>3.71</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>9.1999999999999993</v>
       </c>
@@ -1010,7 +3847,7 @@
         <v>3.41</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>9.3000000000000007</v>
       </c>
@@ -1021,7 +3858,7 @@
         <v>45505</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>9.4</v>
       </c>
@@ -1035,7 +3872,7 @@
         <v>3.36</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>9.5</v>
       </c>
@@ -1049,7 +3886,7 @@
         <v>3.39</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -1063,7 +3900,7 @@
         <v>3.45</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>5.0999999999999996</v>
       </c>
@@ -1077,7 +3914,7 @@
         <v>3.46</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5.2</v>
       </c>
@@ -1091,7 +3928,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>5.3</v>
       </c>
@@ -1105,7 +3942,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>5.4</v>
       </c>
@@ -1122,7 +3959,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>5.5</v>
       </c>
@@ -1136,7 +3973,7 @@
         <v>3.6</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>3.1</v>
       </c>
@@ -1162,7 +3999,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>3.2</v>
       </c>
@@ -1188,7 +4025,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>3.3</v>
       </c>
@@ -1199,7 +4036,7 @@
         <v>45554</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>3.4</v>
       </c>
@@ -1225,7 +4062,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>6.1</v>
       </c>
@@ -1251,7 +4088,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>6.2</v>
       </c>
@@ -1277,7 +4114,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>6.3</v>
       </c>
@@ -1303,7 +4140,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>11</v>
       </c>
@@ -1329,7 +4166,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>9.5</v>
       </c>
@@ -1355,7 +4192,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>9.4</v>
       </c>
@@ -1381,7 +4218,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>9.3000000000000007</v>
       </c>
@@ -1407,7 +4244,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>9.1999999999999993</v>
       </c>
@@ -1433,7 +4270,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>9.1</v>
       </c>
@@ -1444,7 +4281,7 @@
         <v>45554</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>5.0999999999999996</v>
       </c>
@@ -1470,7 +4307,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>5.2</v>
       </c>
@@ -1496,7 +4333,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>5.3</v>
       </c>
@@ -1522,7 +4359,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>5.4</v>
       </c>
@@ -1548,7 +4385,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>5.5</v>
       </c>
@@ -1574,7 +4411,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>5.6</v>
       </c>
@@ -1600,7 +4437,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32">
         <v>9.1</v>
       </c>
@@ -1629,7 +4466,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33">
         <v>9.1999999999999993</v>
       </c>
@@ -1658,7 +4495,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34">
         <v>9.3000000000000007</v>
       </c>
@@ -1687,7 +4524,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35">
         <v>9.4</v>
       </c>
@@ -1716,7 +4553,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36">
         <v>9.5</v>
       </c>
@@ -1745,7 +4582,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>11</v>
       </c>
@@ -1774,7 +4611,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38">
         <v>5.0999999999999996</v>
       </c>
@@ -1788,7 +4625,7 @@
         <v>0.59722222222222221</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39">
         <v>5.2</v>
       </c>
@@ -1802,7 +4639,7 @@
         <v>0.57916666666666672</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40">
         <v>5.3</v>
       </c>
@@ -1816,7 +4653,7 @@
         <v>0.61805555555555558</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41">
         <v>5.4</v>
       </c>
@@ -1827,7 +4664,7 @@
         <v>45638</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42">
         <v>5.5</v>
       </c>
@@ -1838,7 +4675,7 @@
         <v>45638</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43">
         <v>3.1</v>
       </c>
@@ -1867,7 +4704,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44">
         <v>3.2</v>
       </c>
@@ -1896,7 +4733,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45">
         <v>3.4</v>
       </c>
@@ -1925,7 +4762,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46">
         <v>6.1</v>
       </c>
@@ -1954,7 +4791,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47">
         <v>6.2</v>
       </c>
@@ -1983,7 +4820,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48">
         <v>6.3</v>
       </c>
@@ -2012,7 +4849,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A49">
         <v>3.1</v>
       </c>
@@ -2038,7 +4875,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A50">
         <v>3.2</v>
       </c>
@@ -2064,7 +4901,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A51">
         <v>3.4</v>
       </c>
@@ -2090,7 +4927,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A52">
         <v>6.1</v>
       </c>
@@ -2116,7 +4953,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A53">
         <v>6.2</v>
       </c>
@@ -2142,7 +4979,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A54">
         <v>6.3</v>
       </c>
@@ -2168,7 +5005,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>11</v>
       </c>
@@ -2194,7 +5031,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A56">
         <v>9</v>
       </c>
@@ -2220,7 +5057,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A57">
         <v>9.4</v>
       </c>
@@ -2246,7 +5083,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A58">
         <v>9.3000000000000007</v>
       </c>
@@ -2272,7 +5109,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A59">
         <v>9.1999999999999993</v>
       </c>
@@ -2298,7 +5135,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A60">
         <v>9.1</v>
       </c>
@@ -2330,7 +5167,7 @@
         <v>-82.27064</v>
       </c>
     </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A61">
         <v>5.0999999999999996</v>
       </c>
@@ -2356,7 +5193,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A62">
         <v>5.2</v>
       </c>
@@ -2382,7 +5219,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A63">
         <v>5.3</v>
       </c>
@@ -2408,7 +5245,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.75">
+    <row r="64" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A64">
         <v>5.4</v>
       </c>
@@ -2434,7 +5271,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65">
         <v>5</v>
       </c>
@@ -2460,7 +5297,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66">
         <v>6.3</v>
       </c>
@@ -2486,7 +5323,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67">
         <v>3.2</v>
       </c>
@@ -2509,7 +5346,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68">
         <v>6.1</v>
       </c>
@@ -2535,7 +5372,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69">
         <v>6.2</v>
       </c>
@@ -2561,7 +5398,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70">
         <v>3.1</v>
       </c>
@@ -2587,7 +5424,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>11</v>
       </c>
@@ -2613,7 +5450,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72">
         <v>9</v>
       </c>
@@ -2639,7 +5476,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73">
         <v>9.4</v>
       </c>
@@ -2665,7 +5502,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74">
         <v>9.3000000000000007</v>
       </c>
@@ -2691,7 +5528,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75">
         <v>9.1999999999999993</v>
       </c>
@@ -2717,7 +5554,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76">
         <v>9.1</v>
       </c>
@@ -2743,7 +5580,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77">
         <v>5.0999999999999996</v>
       </c>
@@ -2769,7 +5606,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78">
         <v>5.2</v>
       </c>
@@ -2795,7 +5632,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79">
         <v>5.3</v>
       </c>
@@ -2821,7 +5658,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80">
         <v>5.5</v>
       </c>
@@ -2847,7 +5684,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81">
         <v>5.0999999999999996</v>
       </c>
@@ -2876,7 +5713,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82">
         <v>5.2</v>
       </c>
@@ -2905,7 +5742,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83">
         <v>5.3</v>
       </c>
@@ -2934,7 +5771,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84">
         <v>5.4</v>
       </c>
@@ -2963,7 +5800,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.75">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85">
         <v>5.5</v>
       </c>
@@ -2999,31 +5836,51 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BD191BDA-3D26-40F9-AE7E-DB7C188742A6}">
-  <dimension ref="A1:E17"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="2" max="2" width="9.140625" style="3"/>
+    <col min="4" max="4" width="11.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="9.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="3" t="s">
         <v>1</v>
       </c>
       <c r="C1" t="s">
         <v>13</v>
       </c>
       <c r="D1" t="s">
+        <v>16</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
         <v>14</v>
       </c>
-      <c r="E1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="H1" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="I1" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="J1" s="4"/>
+      <c r="K1" s="4"/>
+    </row>
+    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>5</v>
       </c>
-      <c r="B2">
+      <c r="B2" s="3">
         <v>5</v>
       </c>
       <c r="C2">
@@ -3036,12 +5893,19 @@
         <f>D2/$D$2</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F2" s="4">
+        <v>29.861879999999999</v>
+      </c>
+      <c r="G2" s="4">
+        <v>-82.283659999999998</v>
+      </c>
+      <c r="I2" s="4"/>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>5.4</v>
       </c>
-      <c r="B3">
+      <c r="B3" s="3">
         <v>5</v>
       </c>
       <c r="C3">
@@ -3054,12 +5918,21 @@
         <f t="shared" ref="E3:E6" si="0">D3/$D$2</f>
         <v>0.81590896319190787</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F3" s="4">
+        <v>29.872119999999999</v>
+      </c>
+      <c r="G3" s="4">
+        <v>-82.283850000000001</v>
+      </c>
+      <c r="I3" s="4"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>5.3</v>
       </c>
-      <c r="B4">
+      <c r="B4" s="3">
         <v>5</v>
       </c>
       <c r="C4">
@@ -3072,12 +5945,19 @@
         <f t="shared" si="0"/>
         <v>0.57597077830851362</v>
       </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F4" s="4">
+        <v>29.8813</v>
+      </c>
+      <c r="G4" s="4">
+        <v>-82.280479999999997</v>
+      </c>
+      <c r="I4" s="4"/>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>5.2</v>
       </c>
-      <c r="B5">
+      <c r="B5" s="3">
         <v>5</v>
       </c>
       <c r="C5">
@@ -3090,12 +5970,19 @@
         <f t="shared" si="0"/>
         <v>0.10184546220848553</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F5" s="4">
+        <v>29.89631</v>
+      </c>
+      <c r="G5" s="4">
+        <v>-82.273979999999995</v>
+      </c>
+      <c r="I5" s="4"/>
+    </row>
+    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5.0999999999999996</v>
       </c>
-      <c r="B6">
+      <c r="B6" s="3">
         <v>5</v>
       </c>
       <c r="C6">
@@ -3108,12 +5995,19 @@
         <f t="shared" si="0"/>
         <v>7.7760606912053946E-3</v>
       </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F6" s="4">
+        <v>29.903310000000001</v>
+      </c>
+      <c r="G6" s="4">
+        <v>-82.272649999999999</v>
+      </c>
+      <c r="I6" s="4"/>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3.1</v>
       </c>
-      <c r="B7">
+      <c r="B7" s="3">
         <v>6</v>
       </c>
       <c r="C7">
@@ -3126,12 +6020,21 @@
         <f t="shared" ref="E7:E10" si="1">D7/$D$12</f>
         <v>3.4975053104776958E-4</v>
       </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F7" s="4">
+        <v>29.990659999999998</v>
+      </c>
+      <c r="G7" s="4">
+        <v>-82.205830000000006</v>
+      </c>
+      <c r="I7" s="4"/>
+      <c r="J7" s="4"/>
+      <c r="K7" s="4"/>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>3.2</v>
       </c>
-      <c r="B8">
+      <c r="B8" s="3">
         <v>6</v>
       </c>
       <c r="C8">
@@ -3144,12 +6047,19 @@
         <f t="shared" si="1"/>
         <v>5.1508783663108612E-2</v>
       </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F8" s="4">
+        <v>29.987069999999999</v>
+      </c>
+      <c r="G8" s="4">
+        <v>-82.2029</v>
+      </c>
+      <c r="I8" s="4"/>
+    </row>
+    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>3.4</v>
       </c>
-      <c r="B9">
+      <c r="B9" s="3">
         <v>6</v>
       </c>
       <c r="C9">
@@ -3162,12 +6072,19 @@
         <f t="shared" si="1"/>
         <v>4.3303858123795877E-2</v>
       </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F9" s="4">
+        <v>29.975639999999999</v>
+      </c>
+      <c r="G9" s="4">
+        <v>-82.198740000000001</v>
+      </c>
+      <c r="I9" s="4"/>
+    </row>
+    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6.1</v>
       </c>
-      <c r="B10">
+      <c r="B10" s="3">
         <v>6</v>
       </c>
       <c r="C10">
@@ -3180,12 +6097,19 @@
         <f t="shared" si="1"/>
         <v>0.11899726021150711</v>
       </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F10" s="4">
+        <v>29.967690000000001</v>
+      </c>
+      <c r="G10" s="4">
+        <v>-82.1999</v>
+      </c>
+      <c r="I10" s="4"/>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>6.2</v>
       </c>
-      <c r="B11">
+      <c r="B11" s="3">
         <v>6</v>
       </c>
       <c r="C11">
@@ -3198,12 +6122,19 @@
         <f>D11/$D$12</f>
         <v>0.99851800622437381</v>
       </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F11" s="4">
+        <v>29.9434</v>
+      </c>
+      <c r="G11" s="4">
+        <v>-82.188500000000005</v>
+      </c>
+      <c r="I11" s="4"/>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>6.3</v>
       </c>
-      <c r="B12">
+      <c r="B12" s="3">
         <v>6</v>
       </c>
       <c r="C12">
@@ -3216,12 +6147,19 @@
         <f>D12/$D$12</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F12" s="4">
+        <v>29.940349999999999</v>
+      </c>
+      <c r="G12" s="4">
+        <v>-82.188969999999998</v>
+      </c>
+      <c r="I12" s="4"/>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>9</v>
       </c>
-      <c r="B13">
+      <c r="B13" s="3">
         <v>9</v>
       </c>
       <c r="C13">
@@ -3234,12 +6172,19 @@
         <f>D13/$D$13</f>
         <v>1</v>
       </c>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F13" s="4">
+        <v>29.904579999999999</v>
+      </c>
+      <c r="G13" s="4">
+        <v>-82.220770000000002</v>
+      </c>
+      <c r="I13" s="4"/>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>9.4</v>
       </c>
-      <c r="B14">
+      <c r="B14" s="3">
         <v>9</v>
       </c>
       <c r="C14">
@@ -3252,12 +6197,21 @@
         <f t="shared" ref="E14:E17" si="2">D14/$D$13</f>
         <v>0.97000115786771113</v>
       </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F14" s="4">
+        <v>29.9072</v>
+      </c>
+      <c r="G14" s="4">
+        <v>-82.230220000000003</v>
+      </c>
+      <c r="I14" s="4"/>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4"/>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>9.3000000000000007</v>
       </c>
-      <c r="B15">
+      <c r="B15" s="3">
         <v>9</v>
       </c>
       <c r="C15">
@@ -3270,12 +6224,21 @@
         <f t="shared" si="2"/>
         <v>0.29305531083713837</v>
       </c>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F15" s="4">
+        <v>29.912749999999999</v>
+      </c>
+      <c r="G15" s="4">
+        <v>-82.238290000000006</v>
+      </c>
+      <c r="I15" s="4"/>
+      <c r="J15" s="4"/>
+      <c r="K15" s="4"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>9.1999999999999993</v>
       </c>
-      <c r="B16">
+      <c r="B16" s="3">
         <v>9</v>
       </c>
       <c r="C16">
@@ -3288,12 +6251,21 @@
         <f t="shared" si="2"/>
         <v>9.8708725791754978E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
+      <c r="F16" s="4">
+        <v>29.926279999999998</v>
+      </c>
+      <c r="G16" s="4">
+        <v>-82.237170000000006</v>
+      </c>
+      <c r="I16" s="4"/>
+      <c r="J16" s="4"/>
+      <c r="K16" s="4"/>
+    </row>
+    <row r="17" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>9.1</v>
       </c>
-      <c r="B17">
+      <c r="B17" s="3">
         <v>9</v>
       </c>
       <c r="C17">
@@ -3306,8 +6278,23 @@
         <f t="shared" si="2"/>
         <v>1.319933951198393E-2</v>
       </c>
+      <c r="F17" s="4">
+        <v>29.940439999999999</v>
+      </c>
+      <c r="G17" s="4">
+        <v>-82.23903</v>
+      </c>
+      <c r="I17" s="4"/>
+      <c r="J17" s="4"/>
+      <c r="K17" s="4"/>
+    </row>
+    <row r="18" spans="1:11" x14ac:dyDescent="0.25">
+      <c r="I18" s="4"/>
+      <c r="J18" s="4"/>
+      <c r="K18" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
 </file>